--- a/data/legal_entity_mapping.xlsx
+++ b/data/legal_entity_mapping.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Legal Entity(long name)</t>
   </si>
@@ -23,13 +23,25 @@
   </si>
   <si>
     <t>bnp IV RES</t>
+  </si>
+  <si>
+    <t>bnp II wow</t>
+  </si>
+  <si>
+    <t>bnp II w</t>
+  </si>
+  <si>
+    <t>bnp II boom</t>
+  </si>
+  <si>
+    <t>bnp II b</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -41,6 +53,10 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -50,18 +66,35 @@
       <patternFill patternType="lightGray"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border/>
+    <border>
+      <left style="thin">
+        <color rgb="FF9A9A9A"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9A9A9A"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9A9A9A"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9A9A9A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -292,11 +325,27 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
